--- a/coronavirus_response_forms/015_n95_fit_test_form--coronavirus_response_forms.xlsx
+++ b/coronavirus_response_forms/015_n95_fit_test_form--coronavirus_response_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -442,7 +442,7 @@
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
     <col width="40" customWidth="1" min="2" max="2"/>
-    <col width="35" customWidth="1" min="3" max="3"/>
+    <col width="36" customWidth="1" min="3" max="3"/>
     <col width="12" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -743,12 +743,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>participant_fit_tester_rating</t>
+          <t>participant_fit_tester_rating_2</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Participant's Fit Tester Rating</t>
+          <t>Participant Fit Tester Rating 2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -871,7 +871,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Participant N95 Fitting</t>
+          <t>Participant N95 Fitting Rating 2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
@@ -916,7 +916,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>participant_fit_tester_rating_2</t>
+          <t>participant_fit_tester_rating_2_2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -943,12 +943,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>participant_n95_fitting_type</t>
+          <t>participant_n95_fitting_type_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>N95 Fitting Type</t>
+          <t>Participant N95 Fitting Type 2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
@@ -970,12 +970,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>participant_n95_fitting_rating_2</t>
+          <t>participant_n95_fitting_rating_2_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Participant N95 Fitting</t>
+          <t>Participant N95 Fitting Rating 2 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
@@ -1280,7 +1280,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>participant_fit_tester_rating_choices</t>
+          <t>participant_fit_tester_rating_2_choices</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1297,7 +1297,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>participant_fit_tester_rating_choices</t>
+          <t>participant_fit_tester_rating_2_choices</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1382,7 +1382,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>participant_fit_tester_rating_2_choices</t>
+          <t>participant_fit_tester_rating_2_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1399,7 +1399,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>participant_fit_tester_rating_2_choices</t>
+          <t>participant_fit_tester_rating_2_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1416,7 +1416,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>participant_n95_fitting_type_choices</t>
+          <t>participant_n95_fitting_type_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1433,7 +1433,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>participant_n95_fitting_type_choices</t>
+          <t>participant_n95_fitting_type_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1450,7 +1450,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>participant_n95_fitting_rating_2_choices</t>
+          <t>participant_n95_fitting_rating_2_2_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1467,7 +1467,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>participant_n95_fitting_rating_2_choices</t>
+          <t>participant_n95_fitting_rating_2_2_choices</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
